--- a/data/trans_orig/P6711-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6711-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si puede dejar su puesto de trabajo al menos una hora sin tener que pedir un permiso especial si le ha surgido algún asunto personal o familiar en 2012</t>
+          <t>Población según si puede dejar su puesto de trabajo al menos una hora sin tener que pedir un permiso especial si le ha surgido algún asunto personal o familiar en 2012 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26559</t>
+          <t>26498</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49108</t>
+          <t>51091</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14184</t>
+          <t>13475</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33354</t>
+          <t>32527</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44174</t>
+          <t>44208</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75640</t>
+          <t>74704</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18533</t>
+          <t>18179</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18209</t>
+          <t>17998</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>10841</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29854</t>
+          <t>29896</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22147</t>
+          <t>21730</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44187</t>
+          <t>42927</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15995</t>
+          <t>17087</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34344</t>
+          <t>35172</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>42465</t>
+          <t>43713</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>70515</t>
+          <t>69993</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31131</t>
+          <t>32235</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55705</t>
+          <t>55849</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15891</t>
+          <t>16435</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34859</t>
+          <t>34880</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52773</t>
+          <t>53126</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83109</t>
+          <t>84074</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>131642</t>
+          <t>128587</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>163564</t>
+          <t>163992</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>69077</t>
+          <t>68264</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94997</t>
+          <t>94960</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>208078</t>
+          <t>209560</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>248759</t>
+          <t>249725</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>58,05%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39901</t>
+          <t>38950</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68726</t>
+          <t>67101</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23735</t>
+          <t>24467</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46289</t>
+          <t>46926</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69182</t>
+          <t>68406</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105848</t>
+          <t>105735</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13023</t>
+          <t>12511</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32446</t>
+          <t>32229</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>10394</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28888</t>
+          <t>26125</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27662</t>
+          <t>26970</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52177</t>
+          <t>51984</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63265</t>
+          <t>63767</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>97555</t>
+          <t>98355</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>29085</t>
+          <t>28993</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53369</t>
+          <t>53777</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>100641</t>
+          <t>101586</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>144123</t>
+          <t>142750</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48297</t>
+          <t>48997</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77559</t>
+          <t>79953</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37529</t>
+          <t>38351</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65223</t>
+          <t>65243</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94125</t>
+          <t>92935</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134489</t>
+          <t>132440</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>174603</t>
+          <t>170281</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>217229</t>
+          <t>214474</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>107686</t>
+          <t>110475</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>143059</t>
+          <t>144740</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>292283</t>
+          <t>292298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>347023</t>
+          <t>347970</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,18%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16782</t>
+          <t>17260</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38044</t>
+          <t>37147</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14906</t>
+          <t>14256</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33938</t>
+          <t>32578</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36406</t>
+          <t>36669</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64592</t>
+          <t>63581</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14913</t>
+          <t>14986</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35052</t>
+          <t>36668</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10058</t>
+          <t>9609</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26780</t>
+          <t>27884</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28429</t>
+          <t>28684</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55559</t>
+          <t>55115</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54927</t>
+          <t>55925</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>88436</t>
+          <t>89438</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16706</t>
+          <t>16193</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37896</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>76701</t>
+          <t>76723</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>114009</t>
+          <t>117155</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39198</t>
+          <t>39054</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>65072</t>
+          <t>66682</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35635</t>
+          <t>35819</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59659</t>
+          <t>60842</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79417</t>
+          <t>80882</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>115628</t>
+          <t>118715</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>131014</t>
+          <t>130278</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>167692</t>
+          <t>168891</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>86206</t>
+          <t>86472</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>117897</t>
+          <t>116624</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>226499</t>
+          <t>226983</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>275024</t>
+          <t>274831</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>51,49%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32208</t>
+          <t>31977</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57207</t>
+          <t>58746</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39696</t>
+          <t>39057</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66543</t>
+          <t>66286</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78060</t>
+          <t>78671</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>116910</t>
+          <t>115840</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22122</t>
+          <t>21112</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43218</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19230</t>
+          <t>19588</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42087</t>
+          <t>41188</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>47485</t>
+          <t>47691</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>77886</t>
+          <t>78091</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>65932</t>
+          <t>65977</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>99706</t>
+          <t>98336</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37635</t>
+          <t>36655</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>65176</t>
+          <t>63073</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>111059</t>
+          <t>112188</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>153106</t>
+          <t>153883</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88398</t>
+          <t>88553</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>125459</t>
+          <t>125328</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44675</t>
+          <t>45606</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72758</t>
+          <t>72756</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>141993</t>
+          <t>142450</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>188587</t>
+          <t>187895</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>135643</t>
+          <t>132990</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>176779</t>
+          <t>175812</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>95395</t>
+          <t>96045</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>130763</t>
+          <t>131161</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>240026</t>
+          <t>240183</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>293796</t>
+          <t>291739</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,56%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>135140</t>
+          <t>134363</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>187696</t>
+          <t>184469</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>109113</t>
+          <t>111018</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>151900</t>
+          <t>153924</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>261031</t>
+          <t>258775</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>324660</t>
+          <t>323970</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>67807</t>
+          <t>68569</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>104222</t>
+          <t>104647</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>57302</t>
+          <t>57123</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>92366</t>
+          <t>91915</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>135331</t>
+          <t>135989</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>183177</t>
+          <t>184591</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>237508</t>
+          <t>237444</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>297677</t>
+          <t>297501</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>117339</t>
+          <t>119944</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>163264</t>
+          <t>163678</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>369878</t>
+          <t>367005</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>444998</t>
+          <t>441440</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,68%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>234572</t>
+          <t>232702</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>293311</t>
+          <t>290776</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>157693</t>
+          <t>156259</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>208098</t>
+          <t>206109</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>405761</t>
+          <t>403035</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>481282</t>
+          <t>481335</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>609132</t>
+          <t>607701</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>687135</t>
+          <t>683056</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>388759</t>
+          <t>391257</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>456692</t>
+          <t>457061</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1017359</t>
+          <t>1017357</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1120068</t>
+          <t>1118798</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,34%</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si puede dejar su puesto de trabajo al menos una hora sin tener que pedir un permiso especial si le ha surgido algún asunto personal o familiar en 2016</t>
+          <t>Población según si puede dejar su puesto de trabajo al menos una hora sin tener que pedir un permiso especial si le ha surgido algún asunto personal o familiar en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22731</t>
+          <t>22410</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43803</t>
+          <t>44478</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23062</t>
+          <t>23316</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44084</t>
+          <t>42356</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50828</t>
+          <t>50786</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79862</t>
+          <t>81225</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>21084</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42450</t>
+          <t>42476</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12546</t>
+          <t>13100</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29118</t>
+          <t>30021</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38188</t>
+          <t>38212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65839</t>
+          <t>65342</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44005</t>
+          <t>43544</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69104</t>
+          <t>69351</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33841</t>
+          <t>33038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56032</t>
+          <t>54620</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>83609</t>
+          <t>82825</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>117901</t>
+          <t>118452</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51862</t>
+          <t>53250</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80004</t>
+          <t>80881</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22828</t>
+          <t>23544</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43504</t>
+          <t>43371</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82183</t>
+          <t>81781</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115560</t>
+          <t>116638</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45753</t>
+          <t>46015</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72067</t>
+          <t>72679</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28536</t>
+          <t>28938</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50877</t>
+          <t>50202</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>81042</t>
+          <t>81069</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>115314</t>
+          <t>114428</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39787</t>
+          <t>41246</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70236</t>
+          <t>72028</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29474</t>
+          <t>29513</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54097</t>
+          <t>53412</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76102</t>
+          <t>75931</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114636</t>
+          <t>114262</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35496</t>
+          <t>36783</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64179</t>
+          <t>62828</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22542</t>
+          <t>22469</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43139</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64306</t>
+          <t>64941</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>98495</t>
+          <t>100359</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85138</t>
+          <t>85025</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>123937</t>
+          <t>121816</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50062</t>
+          <t>49508</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76700</t>
+          <t>76421</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>143347</t>
+          <t>144576</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>187959</t>
+          <t>188674</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,43%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76237</t>
+          <t>76928</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112505</t>
+          <t>111818</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56749</t>
+          <t>57517</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85735</t>
+          <t>86926</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>143492</t>
+          <t>142104</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>188702</t>
+          <t>190324</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,67%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93978</t>
+          <t>96921</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131874</t>
+          <t>134677</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55488</t>
+          <t>54894</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85466</t>
+          <t>85912</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>158881</t>
+          <t>158561</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>205362</t>
+          <t>207413</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,16%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42835</t>
+          <t>40872</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71062</t>
+          <t>69558</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35785</t>
+          <t>35763</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60536</t>
+          <t>62144</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>84204</t>
+          <t>83686</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123263</t>
+          <t>121441</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49566</t>
+          <t>49364</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78200</t>
+          <t>80129</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50355</t>
+          <t>51176</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>79114</t>
+          <t>78454</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>106972</t>
+          <t>107095</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>149462</t>
+          <t>146954</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71370</t>
+          <t>71265</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>106453</t>
+          <t>105779</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>50433</t>
+          <t>48519</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>77327</t>
+          <t>77629</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>128060</t>
+          <t>129068</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>173127</t>
+          <t>175297</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60854</t>
+          <t>61279</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>93578</t>
+          <t>93322</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28133</t>
+          <t>27886</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50789</t>
+          <t>52666</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>95010</t>
+          <t>95388</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>135693</t>
+          <t>136025</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>66057</t>
+          <t>66838</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>98999</t>
+          <t>100318</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44674</t>
+          <t>44536</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71747</t>
+          <t>71732</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>120847</t>
+          <t>119928</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>162407</t>
+          <t>163351</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53471</t>
+          <t>53817</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82262</t>
+          <t>84486</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59355</t>
+          <t>60499</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90204</t>
+          <t>91785</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>120697</t>
+          <t>120911</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>166937</t>
+          <t>164352</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -6532,12 +6532,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28378</t>
+          <t>28168</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>52128</t>
+          <t>52376</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18833</t>
+          <t>18511</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41135</t>
+          <t>40607</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>51441</t>
+          <t>51708</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>83826</t>
+          <t>83166</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>60851</t>
+          <t>61613</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>92699</t>
+          <t>94313</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>54202</t>
+          <t>54251</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>83507</t>
+          <t>84366</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>123547</t>
+          <t>123740</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>169508</t>
+          <t>168225</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>68371</t>
+          <t>70839</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>102437</t>
+          <t>102415</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52354</t>
+          <t>52719</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>80644</t>
+          <t>81958</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>130325</t>
+          <t>129070</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>172710</t>
+          <t>175489</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6843,12 +6843,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>114959</t>
+          <t>113954</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>153324</t>
+          <t>153648</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>73113</t>
+          <t>73618</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>106123</t>
+          <t>106248</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>197618</t>
+          <t>196812</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>247596</t>
+          <t>245825</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,83%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>183727</t>
+          <t>180100</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>242179</t>
+          <t>235194</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>169379</t>
+          <t>169877</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>218940</t>
+          <t>222754</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>368278</t>
+          <t>368181</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>440988</t>
+          <t>442030</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>159464</t>
+          <t>156051</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>211966</t>
+          <t>208373</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>123325</t>
+          <t>123760</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>167301</t>
+          <t>166296</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>297315</t>
+          <t>294506</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>360440</t>
+          <t>363564</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>289795</t>
+          <t>291182</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>355911</t>
+          <t>353689</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>210541</t>
+          <t>209020</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>263069</t>
+          <t>265192</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>517409</t>
+          <t>517369</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>604552</t>
+          <t>605584</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>287616</t>
+          <t>289026</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>352724</t>
+          <t>355224</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>183184</t>
+          <t>182198</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>234586</t>
+          <t>234512</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>488044</t>
+          <t>486726</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>570849</t>
+          <t>569846</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -7553,12 +7553,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>352342</t>
+          <t>352818</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>421121</t>
+          <t>427127</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>227804</t>
+          <t>224737</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>282490</t>
+          <t>284553</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>595372</t>
+          <t>593646</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>689774</t>
+          <t>686868</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6711-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6711-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26498</t>
+          <t>26417</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51091</t>
+          <t>48935</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13475</t>
+          <t>13806</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32527</t>
+          <t>31956</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44208</t>
+          <t>44676</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74704</t>
+          <t>75258</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18179</t>
+          <t>18511</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17998</t>
+          <t>18228</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10841</t>
+          <t>10632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29896</t>
+          <t>28742</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21730</t>
+          <t>22225</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42927</t>
+          <t>42412</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17087</t>
+          <t>15958</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35172</t>
+          <t>34727</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43713</t>
+          <t>43871</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69993</t>
+          <t>70564</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32235</t>
+          <t>31817</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55849</t>
+          <t>56229</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16435</t>
+          <t>16378</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34880</t>
+          <t>35823</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53126</t>
+          <t>52751</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84074</t>
+          <t>83002</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>128587</t>
+          <t>131193</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>163992</t>
+          <t>164132</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68264</t>
+          <t>68788</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94960</t>
+          <t>94081</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>209560</t>
+          <t>205556</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>249725</t>
+          <t>250719</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,28%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38950</t>
+          <t>38914</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67101</t>
+          <t>67918</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24467</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46926</t>
+          <t>47013</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68406</t>
+          <t>68994</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105735</t>
+          <t>105740</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12511</t>
+          <t>12848</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32229</t>
+          <t>32604</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>10270</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26125</t>
+          <t>27789</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26970</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51984</t>
+          <t>52416</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63767</t>
+          <t>65984</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>98355</t>
+          <t>99533</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28993</t>
+          <t>29694</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53777</t>
+          <t>53017</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>101586</t>
+          <t>101845</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>142750</t>
+          <t>143191</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48997</t>
+          <t>49217</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79953</t>
+          <t>77720</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38351</t>
+          <t>38075</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65243</t>
+          <t>63752</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92935</t>
+          <t>95339</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132440</t>
+          <t>134385</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>170281</t>
+          <t>173177</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>214474</t>
+          <t>213766</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>110475</t>
+          <t>109012</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>144740</t>
+          <t>143119</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>292298</t>
+          <t>295914</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>347970</t>
+          <t>348948</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,32%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>17313</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37147</t>
+          <t>38248</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14256</t>
+          <t>14442</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32578</t>
+          <t>33428</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36669</t>
+          <t>36172</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63581</t>
+          <t>62866</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14986</t>
+          <t>15130</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36668</t>
+          <t>35648</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9609</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27884</t>
+          <t>27226</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28684</t>
+          <t>28573</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55115</t>
+          <t>55643</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>55925</t>
+          <t>56211</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>89438</t>
+          <t>88323</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16193</t>
+          <t>16362</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37187</t>
+          <t>37338</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>76723</t>
+          <t>78023</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>117155</t>
+          <t>116589</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39054</t>
+          <t>39551</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66682</t>
+          <t>65747</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35819</t>
+          <t>33909</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60842</t>
+          <t>59042</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80882</t>
+          <t>80752</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>118715</t>
+          <t>118329</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>130278</t>
+          <t>130481</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>168891</t>
+          <t>166990</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>86472</t>
+          <t>84857</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>116624</t>
+          <t>117866</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>226983</t>
+          <t>225470</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>274831</t>
+          <t>272851</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,11%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31977</t>
+          <t>32417</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58746</t>
+          <t>59714</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39057</t>
+          <t>39811</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66286</t>
+          <t>67584</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78671</t>
+          <t>79354</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>115840</t>
+          <t>115427</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21112</t>
+          <t>22086</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>42489</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19588</t>
+          <t>20320</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41188</t>
+          <t>43021</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>47691</t>
+          <t>47077</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>78091</t>
+          <t>77841</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>65977</t>
+          <t>67055</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>98336</t>
+          <t>102270</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>36655</t>
+          <t>37177</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>63073</t>
+          <t>62418</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>112188</t>
+          <t>111696</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>153883</t>
+          <t>153817</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88553</t>
+          <t>87932</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>125328</t>
+          <t>123276</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>45606</t>
+          <t>44599</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72756</t>
+          <t>73216</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>142450</t>
+          <t>140753</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>187895</t>
+          <t>185676</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,81%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>132990</t>
+          <t>135652</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>175812</t>
+          <t>174080</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>96045</t>
+          <t>93749</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>131161</t>
+          <t>128019</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>240183</t>
+          <t>240310</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>291739</t>
+          <t>293752</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,84%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>134363</t>
+          <t>135957</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>184469</t>
+          <t>182864</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>111018</t>
+          <t>109625</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>153924</t>
+          <t>154316</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>258775</t>
+          <t>260373</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>323970</t>
+          <t>323439</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>68569</t>
+          <t>68244</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>104647</t>
+          <t>104676</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>57123</t>
+          <t>58140</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>91915</t>
+          <t>92767</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>135989</t>
+          <t>136483</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>184591</t>
+          <t>184447</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>237444</t>
+          <t>235039</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>297501</t>
+          <t>296152</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>119944</t>
+          <t>119228</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>163678</t>
+          <t>166245</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>367005</t>
+          <t>370370</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>441440</t>
+          <t>447327</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>232702</t>
+          <t>232387</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>290776</t>
+          <t>291982</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>156259</t>
+          <t>159369</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>206109</t>
+          <t>209895</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>403035</t>
+          <t>406902</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>481335</t>
+          <t>482757</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>607701</t>
+          <t>605113</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>683056</t>
+          <t>686304</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>391257</t>
+          <t>391861</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>457061</t>
+          <t>454007</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1017357</t>
+          <t>1016766</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1118798</t>
+          <t>1120371</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,41%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22410</t>
+          <t>22161</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44478</t>
+          <t>43532</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23316</t>
+          <t>22799</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42356</t>
+          <t>44142</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50786</t>
+          <t>51091</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81225</t>
+          <t>81780</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21084</t>
+          <t>21331</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42476</t>
+          <t>42958</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13100</t>
+          <t>12580</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30021</t>
+          <t>28233</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38212</t>
+          <t>38778</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65342</t>
+          <t>65208</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43544</t>
+          <t>43929</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69351</t>
+          <t>70311</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33038</t>
+          <t>33098</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54620</t>
+          <t>55384</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>82825</t>
+          <t>82243</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118452</t>
+          <t>115997</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53250</t>
+          <t>53162</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80881</t>
+          <t>80297</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23544</t>
+          <t>23551</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43371</t>
+          <t>42263</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81781</t>
+          <t>81830</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116638</t>
+          <t>116651</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46015</t>
+          <t>45464</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72679</t>
+          <t>72813</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28938</t>
+          <t>28982</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50202</t>
+          <t>50744</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>81069</t>
+          <t>81453</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>114428</t>
+          <t>116260</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41246</t>
+          <t>39880</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72028</t>
+          <t>70453</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29513</t>
+          <t>29070</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53412</t>
+          <t>54987</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75931</t>
+          <t>75630</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114262</t>
+          <t>115275</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36783</t>
+          <t>37137</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62828</t>
+          <t>63747</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22469</t>
+          <t>22336</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43139</t>
+          <t>42609</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64941</t>
+          <t>65109</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>100359</t>
+          <t>99280</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>85025</t>
+          <t>86428</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>121816</t>
+          <t>121229</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49508</t>
+          <t>50132</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76421</t>
+          <t>77691</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>144576</t>
+          <t>145309</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>188674</t>
+          <t>192058</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,92%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76928</t>
+          <t>77299</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111818</t>
+          <t>113881</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57517</t>
+          <t>56344</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>86926</t>
+          <t>85266</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>142104</t>
+          <t>143082</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>190324</t>
+          <t>187306</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,23%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96921</t>
+          <t>94398</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>134677</t>
+          <t>133328</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54894</t>
+          <t>55955</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85912</t>
+          <t>85440</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>158561</t>
+          <t>158964</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>207413</t>
+          <t>211376</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,73%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40872</t>
+          <t>40741</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69558</t>
+          <t>70198</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35763</t>
+          <t>35784</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62144</t>
+          <t>59907</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83686</t>
+          <t>85060</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121441</t>
+          <t>123491</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49364</t>
+          <t>49329</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80129</t>
+          <t>80683</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51176</t>
+          <t>52095</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>78454</t>
+          <t>80616</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>107095</t>
+          <t>106909</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>146954</t>
+          <t>147846</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71265</t>
+          <t>70704</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>105779</t>
+          <t>103770</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>48519</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>77629</t>
+          <t>77829</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>129068</t>
+          <t>127599</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>175297</t>
+          <t>170941</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>26,95%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61279</t>
+          <t>60281</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>93322</t>
+          <t>94822</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27886</t>
+          <t>27659</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52666</t>
+          <t>51542</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>95388</t>
+          <t>94736</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>136025</t>
+          <t>135000</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>66838</t>
+          <t>66566</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>100318</t>
+          <t>100364</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44536</t>
+          <t>45088</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71732</t>
+          <t>72245</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>119928</t>
+          <t>118199</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>163351</t>
+          <t>163098</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,71%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53817</t>
+          <t>52577</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84486</t>
+          <t>82493</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60499</t>
+          <t>59630</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91785</t>
+          <t>91067</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>120911</t>
+          <t>119836</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>164352</t>
+          <t>165798</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -6532,12 +6532,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28168</t>
+          <t>28526</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>52376</t>
+          <t>53210</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18511</t>
+          <t>18296</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40607</t>
+          <t>39259</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>51708</t>
+          <t>52463</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>83166</t>
+          <t>84170</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>61613</t>
+          <t>61336</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>94313</t>
+          <t>91826</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>54251</t>
+          <t>55146</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>84366</t>
+          <t>83776</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>123740</t>
+          <t>124222</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>168225</t>
+          <t>168099</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70839</t>
+          <t>69773</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>102415</t>
+          <t>101974</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6773,82 +6773,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>17,39%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>25,42%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>66136</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>52365</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>81291</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>20,32%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>16,09%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>24,98%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>151071</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>128321</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>172298</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>20,79%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>17,66%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>25,53%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>66136</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>52719</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>81958</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>20,32%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>16,2%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>25,18%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>151071</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>129070</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>175489</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>20,79%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>17,76%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>113954</t>
+          <t>114497</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>153648</t>
+          <t>153461</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>73618</t>
+          <t>73357</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>106248</t>
+          <t>106170</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>196812</t>
+          <t>200006</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>245825</t>
+          <t>248671</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,22%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>180100</t>
+          <t>182424</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>235194</t>
+          <t>235679</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>169877</t>
+          <t>169161</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>222754</t>
+          <t>220399</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>368181</t>
+          <t>368616</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>442030</t>
+          <t>442263</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>156051</t>
+          <t>156323</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>208373</t>
+          <t>209598</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>123760</t>
+          <t>123466</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>166296</t>
+          <t>165940</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7264,47 +7264,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
+          <t>11,9%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>16,0%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>325816</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>293347</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>360650</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>13,25%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>11,93%</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>16,03%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>325816</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>294506</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>363564</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>13,25%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>11,97%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>291182</t>
+          <t>292172</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>353689</t>
+          <t>359023</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>209020</t>
+          <t>211917</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>265192</t>
+          <t>266281</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>517369</t>
+          <t>517766</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>605584</t>
+          <t>601500</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>289026</t>
+          <t>288436</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>355224</t>
+          <t>354467</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>182198</t>
+          <t>184257</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>234512</t>
+          <t>236757</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>486726</t>
+          <t>487394</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>569846</t>
+          <t>571347</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -7553,12 +7553,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>352818</t>
+          <t>355631</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>427127</t>
+          <t>425663</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>224737</t>
+          <t>227784</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>284553</t>
+          <t>284347</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>593646</t>
+          <t>598049</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>686868</t>
+          <t>688615</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
